--- a/PatternRecogniser/Reports/report_grok4fast.xlsx
+++ b/PatternRecogniser/Reports/report_grok4fast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmgvol\source\repos\AI-DesignPattern\PatternRecogniser\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BF8261-AC54-4283-B4F5-BDBDD7D206B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F095B13F-437B-419D-9E47-43A79EC24109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
